--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742973</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129743139</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129742790</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129745061</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129745080</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129745025</v>
       </c>
       <c r="B7" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129742993</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129745100</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129742559</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129742582</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129743134</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>78834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R9" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B10" t="n">
-        <v>78834</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R10" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129742559</v>
+        <v>129742582</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462482</v>
+        <v>462478</v>
       </c>
       <c r="R12" t="n">
-        <v>6870946</v>
+        <v>6870941</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742582</v>
+        <v>129742559</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462478</v>
+        <v>462482</v>
       </c>
       <c r="R13" t="n">
-        <v>6870941</v>
+        <v>6870946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742973</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129742790</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129745080</v>
+        <v>129745025</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462443</v>
+        <v>462356</v>
       </c>
       <c r="R6" t="n">
-        <v>6871065</v>
+        <v>6871086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129745025</v>
+        <v>129745080</v>
       </c>
       <c r="B7" t="n">
-        <v>79666</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462356</v>
+        <v>462443</v>
       </c>
       <c r="R7" t="n">
-        <v>6871086</v>
+        <v>6871065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>129742993</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>78834</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R9" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R10" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,7 +1566,7 @@
         <v>129745100</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129742582</v>
+        <v>129742559</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462478</v>
+        <v>462482</v>
       </c>
       <c r="R12" t="n">
-        <v>6870941</v>
+        <v>6870946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742559</v>
+        <v>129742582</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462482</v>
+        <v>462478</v>
       </c>
       <c r="R13" t="n">
-        <v>6870946</v>
+        <v>6870941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1862,7 +1862,7 @@
         <v>129743134</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129745025</v>
+        <v>129745080</v>
       </c>
       <c r="B6" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462356</v>
+        <v>462443</v>
       </c>
       <c r="R6" t="n">
-        <v>6871086</v>
+        <v>6871065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129745080</v>
+        <v>129745025</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462443</v>
+        <v>462356</v>
       </c>
       <c r="R7" t="n">
-        <v>6871065</v>
+        <v>6871086</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R9" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B10" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R10" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R9" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R10" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129742559</v>
+        <v>129742582</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462482</v>
+        <v>462478</v>
       </c>
       <c r="R12" t="n">
-        <v>6870946</v>
+        <v>6870941</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1731,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742582</v>
+        <v>129742559</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462478</v>
+        <v>462482</v>
       </c>
       <c r="R13" t="n">
-        <v>6870941</v>
+        <v>6870946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742973</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129743139</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129742790</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129745061</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129745080</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129745025</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129742993</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>78839</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R9" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R10" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,7 +1566,7 @@
         <v>129745100</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129742582</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129742559</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129743134</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129742582</v>
+        <v>129742559</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462478</v>
+        <v>462482</v>
       </c>
       <c r="R12" t="n">
-        <v>6870941</v>
+        <v>6870946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742559</v>
+        <v>129742582</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462482</v>
+        <v>462478</v>
       </c>
       <c r="R13" t="n">
-        <v>6870946</v>
+        <v>6870941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742973</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129743139</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129742790</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129745061</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129745080</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129745025</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129742993</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129745100</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129742559</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129742582</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129743134</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129745080</v>
+        <v>129745025</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462443</v>
+        <v>462356</v>
       </c>
       <c r="R6" t="n">
-        <v>6871065</v>
+        <v>6871086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129745025</v>
+        <v>129745080</v>
       </c>
       <c r="B7" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462356</v>
+        <v>462443</v>
       </c>
       <c r="R7" t="n">
-        <v>6871086</v>
+        <v>6871065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R9" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B10" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R10" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55854-2025 artfynd.xlsx
+++ b/artfynd/A 55854-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129743311</v>
+        <v>129743171</v>
       </c>
       <c r="B9" t="n">
-        <v>78845</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462423</v>
+        <v>462463</v>
       </c>
       <c r="R9" t="n">
-        <v>6870999</v>
+        <v>6871031</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743171</v>
+        <v>129743311</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1501,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462463</v>
+        <v>462423</v>
       </c>
       <c r="R10" t="n">
-        <v>6871031</v>
+        <v>6870999</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
